--- a/specs/Wiring_2/Wiring_2_spec.xlsx
+++ b/specs/Wiring_2/Wiring_2_spec.xlsx
@@ -6481,7 +6481,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Гнездо FASTON 41450-1 рассчитано на 2.08–5.26 мм², а провод на листах 2-2…2-4, 3-2…3-4, 6-2 — 1 мм². Обжим будет ненадёжным.</t>
+          <t>Гнездо FASTON 41450-1 рассчитано на 2.08–5.26 мм², а провод на листах 2-2…2-4, 3-2…3-4, 6-2, 10-2…10-4 — 1 мм². Обжим будет ненадёжным.</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
